--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run9/epoch_40/per_file_predictions_epoch_40.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run9/epoch_40/per_file_predictions_epoch_40.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="494">
   <si>
     <t>Filename</t>
   </si>
@@ -808,697 +808,694 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9775,0.0019,0.0047,0.0029</t>
-  </si>
-  <si>
-    <t>0.0009,0.0013,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.9916,0.0001,0.0000,0.0052</t>
-  </si>
-  <si>
-    <t>0.1383,0.0004,0.0002,0.9521</t>
+    <t>0.9869,0.0031,0.0023,0.0010</t>
+  </si>
+  <si>
+    <t>0.0003,0.0008,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9950,0.0001,0.0000,0.0027</t>
+  </si>
+  <si>
+    <t>0.9015,0.0003,0.0000,0.0697</t>
+  </si>
+  <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0003,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9995,0.0003,0.0000,0.0000</t>
+    <t>0.9995,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.6456,0.0025,0.3562,0.0013</t>
+  </si>
+  <si>
+    <t>0.0993,0.0040,0.9280,0.0004</t>
+  </si>
+  <si>
+    <t>0.0638,0.0027,0.9515,0.0002</t>
+  </si>
+  <si>
+    <t>0.0530,0.0003,0.9635,0.0002</t>
+  </si>
+  <si>
+    <t>0.9400,0.0060,0.0372,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0033,0.9959,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.1604,0.8826,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.9979,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.2022,0.0003,0.8312,0.0007</t>
+  </si>
+  <si>
+    <t>0.0357,0.0061,0.9445,0.0016</t>
+  </si>
+  <si>
+    <t>0.0060,0.0003,0.9949,0.0001</t>
+  </si>
+  <si>
+    <t>0.0152,0.0026,0.9758,0.0004</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0425,0.0011,0.9639,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.9991,0.0013</t>
+  </si>
+  <si>
+    <t>0.0989,0.8750,0.0088,0.0018</t>
+  </si>
+  <si>
+    <t>0.3444,0.0271,0.6013,0.0008</t>
+  </si>
+  <si>
+    <t>0.0017,0.0113,0.9971,0.0031</t>
+  </si>
+  <si>
+    <t>0.0047,0.5448,0.8644,0.0004</t>
+  </si>
+  <si>
+    <t>0.9890,0.0031,0.0037,0.0004</t>
+  </si>
+  <si>
+    <t>0.9498,0.0113,0.0190,0.0015</t>
+  </si>
+  <si>
+    <t>0.7844,0.3153,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0086,0.9741,0.0489,0.0002</t>
+  </si>
+  <si>
+    <t>0.0389,0.1720,0.7071,0.0025</t>
+  </si>
+  <si>
+    <t>0.1152,0.0016,0.8593,0.0062</t>
+  </si>
+  <si>
+    <t>0.0446,0.0040,0.9396,0.0005</t>
+  </si>
+  <si>
+    <t>0.0082,0.0001,0.9904,0.0004</t>
+  </si>
+  <si>
+    <t>0.0033,0.0255,0.9910,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.9954,0.0073,0.0003</t>
+  </si>
+  <si>
+    <t>0.0007,0.0010,0.9978,0.0009</t>
+  </si>
+  <si>
+    <t>0.0222,0.4400,0.0002,0.8036</t>
+  </si>
+  <si>
+    <t>0.0056,0.9896,0.0049,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0078,0.9978,0.0002</t>
+  </si>
+  <si>
+    <t>0.0011,0.1470,0.9926,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0004,0.9987,0.0018</t>
+  </si>
+  <si>
+    <t>0.0009,0.0013,0.9984,0.0002</t>
+  </si>
+  <si>
+    <t>0.9961,0.0034,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9959,0.0036,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0106,0.9989,0.0019</t>
+  </si>
+  <si>
+    <t>0.9984,0.0015,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9976,0.0024,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9911,0.9750,0.0000</t>
+  </si>
+  <si>
+    <t>0.0028,0.0151,0.9944,0.0001</t>
+  </si>
+  <si>
+    <t>0.0022,0.0113,0.9935,0.0008</t>
+  </si>
+  <si>
+    <t>0.0000,0.9651,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.9990,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.9992,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9586,0.0005,0.0633,0.0001</t>
+  </si>
+  <si>
+    <t>0.0876,0.0018,0.9495,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0033,0.9993,0.0008</t>
+  </si>
+  <si>
+    <t>0.0001,0.9648,0.9821,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9434,0.9941,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9990,0.0132,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9991,0.4072,0.0000</t>
+  </si>
+  <si>
+    <t>0.0336,0.0001,0.0015,0.9849</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0006,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0049,0.0007,0.0029,0.9963</t>
+  </si>
+  <si>
+    <t>0.0052,0.0001,0.0013,0.9973</t>
+  </si>
+  <si>
+    <t>0.0002,0.0006,0.0003,0.9998</t>
+  </si>
+  <si>
+    <t>0.0002,0.9844,0.8400,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9960,0.8725,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9645,0.9717,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.2867,0.9576,0.0010</t>
+  </si>
+  <si>
+    <t>0.0001,0.9702,0.9701,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.8165,0.9371,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0013,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0009,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9977,0.0029,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9981,0.0021,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0013,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0001,0.9989,0.0002</t>
+  </si>
+  <si>
+    <t>0.0030,0.0046,0.9929,0.0023</t>
+  </si>
+  <si>
+    <t>0.9490,0.0009,0.0130,0.0018</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0032,0.9955,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.0139,0.9858,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.2851,0.7973,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.3602,0.0172,0.5355,0.0016</t>
+  </si>
+  <si>
+    <t>0.1353,0.0008,0.8923,0.0005</t>
+  </si>
+  <si>
+    <t>0.1647,0.0473,0.5047,0.0078</t>
+  </si>
+  <si>
+    <t>0.1928,0.0275,0.6058,0.0065</t>
+  </si>
+  <si>
+    <t>0.0752,0.0116,0.0195,0.9087</t>
+  </si>
+  <si>
+    <t>0.0008,0.9960,0.0522,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0000,0.0123</t>
+  </si>
+  <si>
+    <t>0.0000,0.9969,0.9641,0.0000</t>
+  </si>
+  <si>
+    <t>0.0019,0.9979,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.8592,0.1767,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.3269,0.7359,0.0019,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0007,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0614,0.9941,0.0004</t>
+  </si>
+  <si>
+    <t>0.0012,0.2878,0.9917,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0029,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.0007,0.9969,0.0001</t>
+  </si>
+  <si>
+    <t>0.8266,0.0018,0.1539,0.0020</t>
+  </si>
+  <si>
+    <t>0.7260,0.0011,0.3092,0.0006</t>
+  </si>
+  <si>
+    <t>0.0028,0.0003,0.9956,0.0005</t>
+  </si>
+  <si>
+    <t>0.8579,0.0024,0.1481,0.0008</t>
+  </si>
+  <si>
+    <t>0.1115,0.0001,0.0000,0.9780</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0081,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.0000,0.0001,0.9996</t>
+  </si>
+  <si>
+    <t>0.0000,0.9994,0.5365,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0164,0.9827,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9985,0.0002,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9581,0.0642,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.3147,0.0016,0.0002,0.8260</t>
+  </si>
+  <si>
+    <t>0.0033,0.0041,0.9933,0.0009</t>
+  </si>
+  <si>
+    <t>0.9893,0.0002,0.0010,0.0045</t>
+  </si>
+  <si>
+    <t>0.9965,0.0003,0.0002,0.0017</t>
+  </si>
+  <si>
+    <t>0.0117,0.9858,0.0013,0.0003</t>
+  </si>
+  <si>
+    <t>0.9892,0.0029,0.0017,0.0004</t>
+  </si>
+  <si>
+    <t>0.9980,0.0003,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.8558,0.0702,0.0120,0.0008</t>
+  </si>
+  <si>
+    <t>0.9007,0.0216,0.0351,0.0005</t>
+  </si>
+  <si>
+    <t>0.9635,0.0102,0.0113,0.0006</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9981,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9835,0.0136,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.6400,0.4421,0.0021,0.0001</t>
+  </si>
+  <si>
+    <t>0.9697,0.0361,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.0125,0.0109,0.9903,0.0004</t>
+  </si>
+  <si>
+    <t>0.9795,0.0287,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9981,0.0009,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9964,0.0027,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0032,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.9830,0.0109,0.0022,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0021,0.0734,0.9928,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.0003,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0543,0.9951,0.0002</t>
+  </si>
+  <si>
+    <t>0.0019,0.0013,0.9978,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0037,0.0008,0.9962,0.0004</t>
+  </si>
+  <si>
+    <t>0.1872,0.0011,0.8656,0.0001</t>
+  </si>
+  <si>
+    <t>0.2092,0.0010,0.8621,0.0001</t>
+  </si>
+  <si>
+    <t>0.4040,0.0113,0.5413,0.0008</t>
+  </si>
+  <si>
+    <t>0.3025,0.0014,0.7578,0.0002</t>
+  </si>
+  <si>
+    <t>0.0888,0.0436,0.8282,0.0006</t>
+  </si>
+  <si>
+    <t>0.6115,0.0039,0.4246,0.0003</t>
+  </si>
+  <si>
+    <t>0.8807,0.0038,0.0865,0.0034</t>
+  </si>
+  <si>
+    <t>0.0930,0.0025,0.9171,0.0002</t>
+  </si>
+  <si>
+    <t>0.1452,0.8981,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.1455,0.9095,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.8827,0.1811,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9852,0.0243,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0206,0.9836,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9485,0.0245,0.0041,0.0004</t>
+  </si>
+  <si>
+    <t>0.8682,0.0011,0.1425,0.0006</t>
+  </si>
+  <si>
+    <t>0.9524,0.0022,0.0142,0.0019</t>
+  </si>
+  <si>
+    <t>0.1691,0.0110,0.7766,0.0039</t>
+  </si>
+  <si>
+    <t>0.4755,0.0010,0.6062,0.0009</t>
+  </si>
+  <si>
+    <t>0.0002,0.0005,0.9992,0.0044</t>
+  </si>
+  <si>
+    <t>0.0098,0.0036,0.9828,0.0004</t>
+  </si>
+  <si>
+    <t>0.0008,0.0349,0.9959,0.0004</t>
+  </si>
+  <si>
+    <t>0.0067,0.0064,0.9876,0.0007</t>
+  </si>
+  <si>
+    <t>0.0003,0.0051,0.9987,0.0004</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9948,0.0068,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9997,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.8735,0.0016,0.1124,0.0012</t>
-  </si>
-  <si>
-    <t>0.0043,0.0042,0.9945,0.0004</t>
-  </si>
-  <si>
-    <t>0.1164,0.0082,0.8880,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.0009,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.5344,0.0061,0.4475,0.0015</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0057,0.9913,0.0018,0.0003</t>
-  </si>
-  <si>
-    <t>0.0799,0.9353,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9994,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.6877,0.0002,0.4267,0.0002</t>
-  </si>
-  <si>
-    <t>0.5210,0.0005,0.5405,0.0007</t>
-  </si>
-  <si>
-    <t>0.0016,0.0000,0.9983,0.0000</t>
-  </si>
-  <si>
-    <t>0.1239,0.0005,0.8974,0.0001</t>
-  </si>
-  <si>
-    <t>0.0033,0.0004,0.9964,0.0001</t>
-  </si>
-  <si>
-    <t>0.1071,0.0006,0.9142,0.0001</t>
-  </si>
-  <si>
-    <t>0.0049,0.0001,0.9937,0.0009</t>
-  </si>
-  <si>
-    <t>0.6934,0.2180,0.0099,0.0009</t>
-  </si>
-  <si>
-    <t>0.7105,0.1556,0.0370,0.0011</t>
-  </si>
-  <si>
-    <t>0.0010,0.0360,0.9954,0.0152</t>
-  </si>
-  <si>
-    <t>0.0147,0.9387,0.0863,0.0005</t>
-  </si>
-  <si>
-    <t>0.9803,0.0165,0.0008,0.0006</t>
-  </si>
-  <si>
-    <t>0.5613,0.4940,0.0022,0.0007</t>
-  </si>
-  <si>
-    <t>0.8357,0.2470,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0073,0.9850,0.0122,0.0003</t>
-  </si>
-  <si>
-    <t>0.0019,0.9725,0.1061,0.0041</t>
-  </si>
-  <si>
-    <t>0.0018,0.0011,0.9817,0.0353</t>
-  </si>
-  <si>
-    <t>0.0163,0.0081,0.9686,0.0004</t>
-  </si>
-  <si>
-    <t>0.7459,0.0001,0.4127,0.0001</t>
-  </si>
-  <si>
-    <t>0.0023,0.0222,0.9943,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9971,0.0069,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0004,0.9993,0.0002</t>
-  </si>
-  <si>
-    <t>0.0133,0.1144,0.0015,0.9810</t>
-  </si>
-  <si>
-    <t>0.0051,0.9810,0.0263,0.0029</t>
-  </si>
-  <si>
-    <t>0.0004,0.9976,0.0169,0.0004</t>
-  </si>
-  <si>
-    <t>0.0006,0.9988,0.0016,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0023,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.0531,0.9952,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9995,0.0002</t>
-  </si>
-  <si>
-    <t>0.0010,0.0001,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0006,0.9984,0.0001</t>
-  </si>
-  <si>
-    <t>0.0028,0.0015,0.9954,0.0003</t>
-  </si>
-  <si>
-    <t>0.9977,0.0014,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9940,0.0069,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0149,0.9990,0.0011</t>
-  </si>
-  <si>
-    <t>0.9980,0.0023,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9869,0.0175,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.8725,0.9152,0.0001</t>
-  </si>
-  <si>
-    <t>0.0040,0.0026,0.9933,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.0038,0.9973,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9658,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0003,0.9988,0.0005</t>
-  </si>
-  <si>
-    <t>0.0007,0.9986,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9728,0.0005,0.0387,0.0001</t>
-  </si>
-  <si>
-    <t>0.0400,0.0008,0.9776,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.0120,0.9987,0.0009</t>
-  </si>
-  <si>
-    <t>0.0003,0.7019,0.9892,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9329,0.9874,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9992,0.0323,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9992,0.9567,0.0000</t>
-  </si>
-  <si>
-    <t>0.0018,0.0001,0.0005,0.9989</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0013,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0049,0.0026,0.0010,0.9970</t>
-  </si>
-  <si>
-    <t>0.0033,0.0007,0.0011,0.9974</t>
-  </si>
-  <si>
-    <t>0.0003,0.0004,0.0005,0.9997</t>
-  </si>
-  <si>
-    <t>0.0003,0.9788,0.8335,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9934,0.8330,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9510,0.9306,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.3882,0.9913,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.9297,0.9736,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9934,0.8842,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0016,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0024,0.0005,0.9978,0.0002</t>
-  </si>
-  <si>
-    <t>0.0015,0.0018,0.9976,0.0005</t>
-  </si>
-  <si>
-    <t>0.9596,0.0004,0.0230,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9996,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0070,0.9916,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.0076,0.9917,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.2714,0.8197,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0892,0.0055,0.8974,0.0009</t>
-  </si>
-  <si>
-    <t>0.1762,0.0006,0.8809,0.0001</t>
-  </si>
-  <si>
-    <t>0.8197,0.0162,0.0907,0.0034</t>
-  </si>
-  <si>
-    <t>0.2431,0.3445,0.0444,0.0326</t>
-  </si>
-  <si>
-    <t>0.0246,0.0141,0.0344,0.9507</t>
-  </si>
-  <si>
-    <t>0.0018,0.9951,0.0147,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0054</t>
-  </si>
-  <si>
-    <t>0.0000,0.9967,0.9783,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.9981,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.7316,0.1482,0.0304,0.0001</t>
-  </si>
-  <si>
-    <t>0.6410,0.3975,0.0032,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0001,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0010,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.5043,0.9912,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.3088,0.9957,0.0000</t>
-  </si>
-  <si>
-    <t>0.0037,0.0083,0.9932,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.0002,0.9974,0.0001</t>
-  </si>
-  <si>
-    <t>0.8989,0.0005,0.1258,0.0004</t>
-  </si>
-  <si>
-    <t>0.5516,0.0009,0.4313,0.0036</t>
-  </si>
-  <si>
-    <t>0.0505,0.0002,0.9608,0.0004</t>
-  </si>
-  <si>
-    <t>0.4287,0.0020,0.6278,0.0012</t>
-  </si>
-  <si>
-    <t>0.3931,0.0003,0.0000,0.7661</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0044,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0015,0.0001,0.0002,0.9994</t>
-  </si>
-  <si>
-    <t>0.0000,0.9976,0.6350,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0599,0.9504,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9984,0.0003,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9455,0.0783,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.1774,0.0002,0.0000,0.9536</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0041,0.0077,0.9909,0.0013</t>
-  </si>
-  <si>
-    <t>0.8984,0.0003,0.0058,0.0656</t>
-  </si>
-  <si>
-    <t>0.9924,0.0025,0.0016,0.0009</t>
-  </si>
-  <si>
-    <t>0.3603,0.7240,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9876,0.0036,0.0025,0.0006</t>
-  </si>
-  <si>
-    <t>0.9927,0.0014,0.0023,0.0002</t>
-  </si>
-  <si>
-    <t>0.8812,0.0353,0.0276,0.0017</t>
-  </si>
-  <si>
-    <t>0.7881,0.0045,0.2219,0.0002</t>
-  </si>
-  <si>
-    <t>0.9361,0.0260,0.0113,0.0009</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9889,0.0086,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.5837,0.4445,0.0040,0.0001</t>
-  </si>
-  <si>
-    <t>0.9706,0.0232,0.0028,0.0002</t>
-  </si>
-  <si>
-    <t>0.0170,0.0691,0.9792,0.0004</t>
-  </si>
-  <si>
-    <t>0.9970,0.0030,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0013,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0006,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.8408,0.2360,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0022,0.9996,0.0002</t>
-  </si>
-  <si>
-    <t>0.9953,0.0021,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0017,0.0002,0.9987,0.0000</t>
-  </si>
-  <si>
-    <t>0.0078,0.0050,0.9880,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0050,0.9980,0.0003</t>
-  </si>
-  <si>
-    <t>0.0010,0.0030,0.9987,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0004,0.9994,0.0012</t>
-  </si>
-  <si>
-    <t>0.0144,0.0017,0.9840,0.0002</t>
-  </si>
-  <si>
-    <t>0.0686,0.0036,0.9328,0.0010</t>
-  </si>
-  <si>
-    <t>0.0435,0.0109,0.9251,0.0038</t>
-  </si>
-  <si>
-    <t>0.5754,0.0011,0.5335,0.0001</t>
-  </si>
-  <si>
-    <t>0.0610,0.0096,0.9260,0.0003</t>
-  </si>
-  <si>
-    <t>0.6521,0.0042,0.3737,0.0005</t>
-  </si>
-  <si>
-    <t>0.8857,0.0027,0.1145,0.0008</t>
-  </si>
-  <si>
-    <t>0.0443,0.0076,0.9394,0.0017</t>
-  </si>
-  <si>
-    <t>0.6231,0.4903,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.0021,0.9976,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.8512,0.2236,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9963,0.0046,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9887,0.0162,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.8944,0.0367,0.0165,0.0007</t>
-  </si>
-  <si>
-    <t>0.8708,0.0008,0.1493,0.0006</t>
-  </si>
-  <si>
-    <t>0.9663,0.0023,0.0157,0.0010</t>
-  </si>
-  <si>
-    <t>0.4029,0.0060,0.5694,0.0021</t>
-  </si>
-  <si>
-    <t>0.6652,0.0037,0.2364,0.0231</t>
-  </si>
-  <si>
-    <t>0.0020,0.0014,0.9964,0.0016</t>
-  </si>
-  <si>
-    <t>0.0015,0.0382,0.9933,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.0097,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0056,0.0017,0.9903,0.0004</t>
-  </si>
-  <si>
-    <t>0.0004,0.0129,0.9979,0.0003</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0010,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0005,0.9990,0.0006</t>
-  </si>
-  <si>
-    <t>0.6128,0.0539,0.1608,0.0030</t>
-  </si>
-  <si>
-    <t>0.9036,0.0009,0.0834,0.0028</t>
-  </si>
-  <si>
-    <t>0.0004,0.0019,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0022,0.9998,0.0008</t>
-  </si>
-  <si>
-    <t>0.0002,0.1134,0.9973,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0005,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.0019,0.9974,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0032,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0048,0.0021,0.9920,0.0001</t>
-  </si>
-  <si>
-    <t>0.0036,0.0037,0.9917,0.0010</t>
-  </si>
-  <si>
-    <t>0.2606,0.0006,0.8143,0.0003</t>
-  </si>
-  <si>
-    <t>0.0628,0.0008,0.9305,0.0023</t>
-  </si>
-  <si>
-    <t>0.9515,0.0004,0.0385,0.0005</t>
-  </si>
-  <si>
-    <t>0.9990,0.0012,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0013,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0225,0.0078,0.9620,0.0004</t>
-  </si>
-  <si>
-    <t>0.0012,0.0008,0.9976,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0067,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0112,0.0041,0.9795,0.0006</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0066,0.0016,0.9897,0.0005</t>
-  </si>
-  <si>
-    <t>0.0166,0.0040,0.9738,0.0028</t>
-  </si>
-  <si>
-    <t>0.0062,0.0012,0.9884,0.0017</t>
-  </si>
-  <si>
-    <t>0.9718,0.0000,0.0003,0.0265</t>
-  </si>
-  <si>
-    <t>0.0008,0.0075,0.0000,0.9995</t>
-  </si>
-  <si>
-    <t>0.0138,0.0009,0.0005,0.9951</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.2833,0.0028,0.0009,0.7753</t>
+    <t>0.0013,0.0018,0.9971,0.0013</t>
+  </si>
+  <si>
+    <t>0.0674,0.0472,0.8728,0.0010</t>
+  </si>
+  <si>
+    <t>0.8908,0.0060,0.0749,0.0053</t>
+  </si>
+  <si>
+    <t>0.0001,0.0010,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0007,0.9998,0.0043</t>
+  </si>
+  <si>
+    <t>0.0000,0.1227,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0003,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0032,0.9981,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0083,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0104,0.0026,0.9839,0.0003</t>
+  </si>
+  <si>
+    <t>0.0077,0.0061,0.9847,0.0009</t>
+  </si>
+  <si>
+    <t>0.8234,0.0025,0.1889,0.0005</t>
+  </si>
+  <si>
+    <t>0.6477,0.0002,0.4082,0.0012</t>
+  </si>
+  <si>
+    <t>0.9599,0.0005,0.0324,0.0004</t>
+  </si>
+  <si>
+    <t>0.9983,0.0013,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9982,0.0011,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0008,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0031,0.0027,0.9946,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0030,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0366,0.9978,0.0001</t>
+  </si>
+  <si>
+    <t>0.0046,0.0278,0.9834,0.0010</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9996,0.0003</t>
+  </si>
+  <si>
+    <t>0.0040,0.0015,0.9940,0.0002</t>
+  </si>
+  <si>
+    <t>0.0322,0.0294,0.9289,0.0014</t>
+  </si>
+  <si>
+    <t>0.0533,0.0483,0.7494,0.0125</t>
+  </si>
+  <si>
+    <t>0.9480,0.0001,0.0001,0.0594</t>
+  </si>
+  <si>
+    <t>0.0013,0.0061,0.0001,0.9992</t>
+  </si>
+  <si>
+    <t>0.0724,0.0011,0.0003,0.9751</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.6995,0.0013,0.0008,0.3128</t>
   </si>
 </sst>
 </file>
@@ -1923,7 +1920,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -1996,7 +1993,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2010,7 +2007,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2024,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2038,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2052,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2066,7 +2063,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2080,7 +2077,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2094,7 +2091,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2108,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2122,7 +2119,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2136,7 +2133,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2150,7 +2147,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2164,7 +2161,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2178,7 +2175,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2189,10 +2186,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2206,7 +2203,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2220,7 +2217,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2234,7 +2231,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2248,7 +2245,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2262,7 +2259,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2276,7 +2273,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2287,10 +2284,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2301,10 +2298,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2318,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2329,10 +2326,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2346,7 +2343,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2360,7 +2357,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2374,7 +2371,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2388,7 +2385,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2399,10 +2396,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2416,7 +2413,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2430,7 +2427,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2441,10 +2438,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2458,7 +2455,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2472,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2486,7 +2483,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2500,7 +2497,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2514,7 +2511,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2528,7 +2525,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2542,7 +2539,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2556,7 +2553,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2570,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2584,7 +2581,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2598,7 +2595,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2612,7 +2609,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2626,7 +2623,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2640,7 +2637,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2654,7 +2651,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2668,7 +2665,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2682,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2710,7 +2707,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2724,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2738,7 +2735,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2752,7 +2749,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2766,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2780,7 +2777,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2794,7 +2791,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2808,7 +2805,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2822,7 +2819,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2836,7 +2833,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2850,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2864,7 +2861,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2878,7 +2875,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2892,7 +2889,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2906,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2917,10 +2914,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2934,7 +2931,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2948,7 +2945,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2962,7 +2959,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2976,7 +2973,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2990,7 +2987,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3004,7 +3001,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3018,7 +3015,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3032,7 +3029,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3046,7 +3043,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3060,7 +3057,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3074,7 +3071,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3088,7 +3085,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3102,7 +3099,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3116,7 +3113,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3130,7 +3127,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3144,7 +3141,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3158,7 +3155,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3172,7 +3169,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>353</v>
+        <v>268</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3200,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3214,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3228,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>273</v>
+        <v>319</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3242,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3256,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3270,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3284,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3298,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>356</v>
+        <v>319</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3312,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3326,7 +3323,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3340,7 +3337,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3354,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3368,7 +3365,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3382,7 +3379,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3396,7 +3393,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>362</v>
+        <v>281</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3505,7 +3502,7 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D118" t="s">
         <v>370</v>
@@ -3519,7 +3516,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
         <v>371</v>
@@ -3564,7 +3561,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3578,7 +3575,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3592,7 +3589,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3606,7 +3603,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3620,7 +3617,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3631,10 +3628,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3648,7 +3645,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>272</v>
+        <v>379</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3662,7 +3659,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>273</v>
+        <v>380</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3676,7 +3673,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>273</v>
+        <v>319</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3690,7 +3687,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3704,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3746,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3757,10 +3754,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3774,7 +3771,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3788,7 +3785,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3802,7 +3799,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3816,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3830,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3844,7 +3841,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3855,10 +3852,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3872,7 +3869,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3886,7 +3883,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3900,7 +3897,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3914,7 +3911,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3928,7 +3925,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3942,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3956,7 +3953,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3970,7 +3967,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3984,7 +3981,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3998,7 +3995,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4012,7 +4009,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4026,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>404</v>
+        <v>319</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4040,7 +4037,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4054,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4068,7 +4065,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4082,7 +4079,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4096,7 +4093,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4110,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4124,7 +4121,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4138,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4152,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4166,7 +4163,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>381</v>
+        <v>319</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4180,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>273</v>
+        <v>412</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4194,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4222,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>384</v>
+        <v>272</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4264,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>273</v>
+        <v>401</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4625,7 +4622,7 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
         <v>442</v>
@@ -4681,7 +4678,7 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
         <v>446</v>
@@ -4751,7 +4748,7 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
         <v>451</v>
@@ -4838,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>457</v>
+        <v>401</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4852,7 +4849,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4866,7 +4863,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4880,7 +4877,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>460</v>
+        <v>269</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4894,7 +4891,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>461</v>
+        <v>319</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4908,7 +4905,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4922,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>272</v>
+        <v>460</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4936,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>273</v>
+        <v>461</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4950,7 +4947,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4961,10 +4958,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4978,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4992,7 +4989,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5006,7 +5003,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5020,7 +5017,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5034,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5048,7 +5045,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5062,7 +5059,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5076,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5090,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5101,10 +5098,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5115,10 +5112,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5132,7 +5129,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5146,7 +5143,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5160,7 +5157,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>350</v>
+        <v>319</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5174,7 +5171,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>477</v>
+        <v>273</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5188,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5202,7 +5199,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5216,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>350</v>
+        <v>478</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5230,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5244,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>268</v>
+        <v>319</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5258,7 +5255,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5272,7 +5269,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5286,7 +5283,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5300,7 +5297,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5314,7 +5311,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5328,7 +5325,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5342,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5356,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5370,7 +5367,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5384,7 +5381,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5398,7 +5395,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5412,7 +5409,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5426,7 +5423,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5437,10 +5434,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>
